--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_2.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01188264397573943</v>
+        <v>0.004763188830600461</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008402787308176896</v>
+        <v>0.008402251151435237</v>
       </c>
       <c r="C2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9514664</v>
+        <v>4816906</v>
       </c>
       <c r="L2" t="n">
-        <v>5735775</v>
+        <v>2963690</v>
       </c>
       <c r="M2" t="n">
-        <v>1495712</v>
+        <v>780311</v>
       </c>
       <c r="N2" t="n">
-        <v>89675</v>
+        <v>45049</v>
       </c>
       <c r="O2" t="n">
-        <v>877453</v>
+        <v>458095</v>
       </c>
       <c r="P2" t="n">
-        <v>348087</v>
+        <v>179561</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999910593032837</v>
+        <v>0.9999865889549255</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9364022016525269</v>
+        <v>0.9505248069763184</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8638634085655212</v>
+        <v>0.8899496793746948</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8103291392326355</v>
+        <v>0.8619515895843506</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6362230181694031</v>
+        <v>0.7008681297302246</v>
       </c>
       <c r="V2" t="n">
-        <v>0.861370325088501</v>
+        <v>0.9004501104354858</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9014411568641663</v>
+        <v>0.9282996654510498</v>
       </c>
       <c r="X2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9738416</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5978550</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1603341</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>118358</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>918488</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360037</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.956718921661377</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911195695400238</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580697178840637</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.662520706653595</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901969313621521</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314232468605042</v>
+        <v>0.931419849395752</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002780992383734829</v>
+        <v>0.001065386208576997</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002013083763574795</v>
+        <v>0.002013410135496696</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9514664</v>
+        <v>4816906</v>
       </c>
       <c r="E3" t="n">
-        <v>630444</v>
+        <v>247349</v>
       </c>
       <c r="F3" t="n">
-        <v>18681</v>
+        <v>4265</v>
       </c>
       <c r="G3" t="n">
-        <v>4758</v>
+        <v>684</v>
       </c>
       <c r="H3" t="n">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="I3" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>20192124</v>
+        <v>10069535</v>
       </c>
       <c r="K3" t="n">
-        <v>22103263</v>
+        <v>11095971</v>
       </c>
       <c r="L3" t="n">
-        <v>25444905</v>
+        <v>12774650</v>
       </c>
       <c r="M3" t="n">
-        <v>30698728</v>
+        <v>15357317</v>
       </c>
       <c r="N3" t="n">
-        <v>32688343</v>
+        <v>16307508</v>
       </c>
       <c r="O3" t="n">
-        <v>31758406</v>
+        <v>15856162</v>
       </c>
       <c r="P3" t="n">
-        <v>32493759</v>
+        <v>16208849</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9356604814529419</v>
+        <v>0.9502099752426147</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8730793595314026</v>
+        <v>0.9049813747406006</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8000273704528809</v>
+        <v>0.8357102274894714</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5015857219696045</v>
+        <v>0.5046659111976624</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8612815737724304</v>
+        <v>0.8996490240097046</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9004198312759399</v>
+        <v>0.9290104508399963</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9738416</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>399532</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17188</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13642</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20192238</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22308915</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25766144</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30783621</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32679327</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31799798</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32505309</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576639533042908</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100337028503418</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575960397720337</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6620204448699951</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015603065490723</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313316941261292</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03926528895598366</v>
+        <v>0.01906294169173491</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03182118993392174</v>
+        <v>0.03181825301110282</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>609357</v>
+        <v>235178</v>
       </c>
       <c r="E4" t="n">
-        <v>5735775</v>
+        <v>2963690</v>
       </c>
       <c r="F4" t="n">
-        <v>210973</v>
+        <v>73507</v>
       </c>
       <c r="G4" t="n">
-        <v>5829</v>
+        <v>1265</v>
       </c>
       <c r="H4" t="n">
-        <v>7174</v>
+        <v>1150</v>
       </c>
       <c r="I4" t="n">
-        <v>482</v>
+        <v>71</v>
       </c>
       <c r="J4" t="n">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="K4" t="n">
-        <v>646209</v>
+        <v>250722</v>
       </c>
       <c r="L4" t="n">
-        <v>903903</v>
+        <v>366487</v>
       </c>
       <c r="M4" t="n">
-        <v>350096</v>
+        <v>124973</v>
       </c>
       <c r="N4" t="n">
-        <v>51274</v>
+        <v>19227</v>
       </c>
       <c r="O4" t="n">
-        <v>141218</v>
+        <v>50645</v>
       </c>
       <c r="P4" t="n">
-        <v>38058</v>
+        <v>13869</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999955296516418</v>
+        <v>0.9999932646751404</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9360312223434448</v>
+        <v>0.9503673911094666</v>
       </c>
       <c r="S4" t="n">
-        <v>0.868446946144104</v>
+        <v>0.8974025249481201</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8051453232765198</v>
+        <v>0.848628044128418</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5609384775161743</v>
+        <v>0.5868009328842163</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8613259196281433</v>
+        <v>0.9000493884086609</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9009301662445068</v>
+        <v>0.9286549687385559</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>411369</v>
+        <v>204986</v>
       </c>
       <c r="Z4" t="n">
-        <v>5978550</v>
+        <v>2980268</v>
       </c>
       <c r="AA4" t="n">
-        <v>166219</v>
+        <v>82895</v>
       </c>
       <c r="AB4" t="n">
-        <v>11022</v>
+        <v>5498</v>
       </c>
       <c r="AC4" t="n">
-        <v>2296</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>440557</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>582664</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>265203</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60290</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99826</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571911692619324</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106143116950989</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578327894210815</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622704863548279</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017647504806519</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313774704933167</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>21345</v>
+        <v>9386</v>
       </c>
       <c r="E5" t="n">
-        <v>246453</v>
+        <v>105251</v>
       </c>
       <c r="F5" t="n">
-        <v>1495712</v>
+        <v>780311</v>
       </c>
       <c r="G5" t="n">
-        <v>21967</v>
+        <v>9069</v>
       </c>
       <c r="H5" t="n">
-        <v>80954</v>
+        <v>29004</v>
       </c>
       <c r="I5" t="n">
-        <v>3140</v>
+        <v>688</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>654264</v>
+        <v>252401</v>
       </c>
       <c r="L5" t="n">
-        <v>833817</v>
+        <v>311173</v>
       </c>
       <c r="M5" t="n">
-        <v>373864</v>
+        <v>153399</v>
       </c>
       <c r="N5" t="n">
-        <v>89108</v>
+        <v>44216</v>
       </c>
       <c r="O5" t="n">
-        <v>141323</v>
+        <v>51098</v>
       </c>
       <c r="P5" t="n">
-        <v>38496</v>
+        <v>13721</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999996542930603</v>
+        <v>0.9999948143959045</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9604940414428711</v>
+        <v>0.9693516492843628</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9472112655639648</v>
+        <v>0.9587195515632629</v>
       </c>
       <c r="T5" t="n">
-        <v>0.978007435798645</v>
+        <v>0.9830426573753357</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9957354664802551</v>
+        <v>0.9961352944374084</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9914169311523438</v>
+        <v>0.9938021898269653</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976744055747986</v>
+        <v>0.9983193278312683</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16114</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>170607</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1603341</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19925</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58323</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>430512</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>591042</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>266235</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60425</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100288</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26546</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735385179519653</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643449783325195</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838559031486511</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963328838348389</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939209222793579</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983882904052734</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>15426</v>
+        <v>6125</v>
       </c>
       <c r="E6" t="n">
-        <v>20565</v>
+        <v>12970</v>
       </c>
       <c r="F6" t="n">
-        <v>34840</v>
+        <v>17229</v>
       </c>
       <c r="G6" t="n">
-        <v>89675</v>
+        <v>45049</v>
       </c>
       <c r="H6" t="n">
-        <v>16941</v>
+        <v>7392</v>
       </c>
       <c r="I6" t="n">
-        <v>1314</v>
+        <v>489</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12962</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10739</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21783</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>118358</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13979</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>6088</v>
+        <v>820</v>
       </c>
       <c r="F7" t="n">
-        <v>84053</v>
+        <v>29631</v>
       </c>
       <c r="G7" t="n">
-        <v>18027</v>
+        <v>7988</v>
       </c>
       <c r="H7" t="n">
-        <v>877453</v>
+        <v>458095</v>
       </c>
       <c r="I7" t="n">
-        <v>33069</v>
+        <v>12603</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1624</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59353</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15171</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>918488</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>1549</v>
+        <v>341</v>
       </c>
       <c r="G8" t="n">
-        <v>693</v>
+        <v>221</v>
       </c>
       <c r="H8" t="n">
-        <v>35823</v>
+        <v>13015</v>
       </c>
       <c r="I8" t="n">
-        <v>348087</v>
+        <v>179561</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25138</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360037</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
